--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$2:$H$13</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -76,6 +79,21 @@
   </si>
   <si>
     <t>Estado</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>Control 2</t>
+  </si>
+  <si>
+    <t>Corregir TP3 y TP4</t>
+  </si>
+  <si>
+    <t>Desaprobado</t>
+  </si>
+  <si>
+    <t>Ausente - no presenta TPs.</t>
   </si>
 </sst>
 </file>
@@ -99,7 +117,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,6 +127,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -125,10 +155,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -411,22 +447,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:E13"/>
+  <dimension ref="B1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.5703125" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E1" s="3"/>
+      <c r="G1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -439,8 +486,14 @@
       <c r="E2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1</v>
       </c>
@@ -450,8 +503,14 @@
       <c r="D3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>2</v>
       </c>
@@ -461,8 +520,14 @@
       <c r="D4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>3</v>
       </c>
@@ -475,8 +540,14 @@
       <c r="E5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>4</v>
       </c>
@@ -486,8 +557,14 @@
       <c r="D6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>5</v>
       </c>
@@ -497,8 +574,14 @@
       <c r="D7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>6</v>
       </c>
@@ -508,8 +591,14 @@
       <c r="D8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>7</v>
       </c>
@@ -522,8 +611,14 @@
       <c r="E9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>8</v>
       </c>
@@ -533,8 +628,14 @@
       <c r="D10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>9</v>
       </c>
@@ -544,8 +645,14 @@
       <c r="D11" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>10</v>
       </c>
@@ -555,8 +662,14 @@
       <c r="D12" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>11</v>
       </c>
@@ -566,10 +679,19 @@
       <c r="D13" t="s">
         <v>17</v>
       </c>
+      <c r="G13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <autoFilter ref="B2:H13"/>
+  <mergeCells count="3">
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11FBC24-0C5B-46AA-8B54-7A2D9AC44F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -85,9 +86,6 @@
   </si>
   <si>
     <t>Control 2</t>
-  </si>
-  <si>
-    <t>Corregir TP3 y TP4</t>
   </si>
   <si>
     <t>Desaprobado</t>
@@ -99,8 +97,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +114,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +148,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -155,18 +167,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,32 +460,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="3.5703125" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="4"/>
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="G1" s="4" t="s">
+      <c r="E1" s="2"/>
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -560,25 +574,27 @@
       <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
@@ -594,8 +610,8 @@
       <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="H8" t="s">
-        <v>22</v>
+      <c r="H8" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
@@ -631,8 +647,8 @@
       <c r="G10" t="s">
         <v>16</v>
       </c>
-      <c r="H10" t="s">
-        <v>22</v>
+      <c r="H10" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
@@ -648,8 +664,8 @@
       <c r="G11" t="s">
         <v>17</v>
       </c>
-      <c r="H11" t="s">
-        <v>22</v>
+      <c r="H11" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
@@ -665,7 +681,7 @@
       <c r="G12" t="s">
         <v>16</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="5" t="s">
         <v>21</v>
       </c>
     </row>
@@ -679,15 +695,15 @@
       <c r="D13" t="s">
         <v>17</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="5" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H13"/>
+  <autoFilter ref="B2:H13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11FBC24-0C5B-46AA-8B54-7A2D9AC44F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$2:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$B$2:$H$14</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="29">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -92,13 +91,31 @@
   </si>
   <si>
     <t>Ausente - no presenta TPs.</t>
+  </si>
+  <si>
+    <t>17.06.2026</t>
+  </si>
+  <si>
+    <t>PRESENTE</t>
+  </si>
+  <si>
+    <t>AUSENTE</t>
+  </si>
+  <si>
+    <t>Evaluación 1</t>
+  </si>
+  <si>
+    <t>Ejercicio 01</t>
+  </si>
+  <si>
+    <t>Ejercicio 02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,8 +139,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +184,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -167,9 +203,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -179,8 +217,14 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,254 +504,376 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="3.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="24.85546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="4"/>
+      <c r="G1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H1" s="5"/>
+      <c r="J1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3">
+      <c r="J2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4">
+      <c r="H4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5">
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6">
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="6">
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8">
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9">
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10">
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11">
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>9</v>
       </c>
-      <c r="D11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12">
+      <c r="H12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13">
         <v>10</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>10</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="G14" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="H14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="12" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B2:H13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="3">
+  <autoFilter ref="B2:H14"/>
+  <mergeCells count="5">
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="35">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -109,6 +109,24 @@
   </si>
   <si>
     <t>Ejercicio 02</t>
+  </si>
+  <si>
+    <t>Ejercicio</t>
+  </si>
+  <si>
+    <t>Evaluación 2</t>
+  </si>
+  <si>
+    <t>24.06.2026</t>
+  </si>
+  <si>
+    <t>10 (Excelente)</t>
+  </si>
+  <si>
+    <t>8 (Excelente)</t>
+  </si>
+  <si>
+    <t>9 (Muy bien)</t>
   </si>
 </sst>
 </file>
@@ -153,7 +171,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,6 +208,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -203,11 +227,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -220,11 +249,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L14"/>
+  <dimension ref="B1:O14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -518,28 +546,35 @@
     <col min="9" max="9" width="0" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9"/>
+      <c r="G1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="10"/>
+      <c r="J1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-    </row>
-    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+    </row>
+    <row r="2" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -558,21 +593,29 @@
       <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+    </row>
+    <row r="3" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="N3" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -591,14 +634,20 @@
       <c r="J4" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -617,14 +666,20 @@
       <c r="J5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -646,14 +701,20 @@
       <c r="J6" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -672,14 +733,20 @@
       <c r="J7" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>5</v>
       </c>
@@ -700,14 +767,17 @@
       <c r="J8" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -726,14 +796,17 @@
       <c r="J9" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
@@ -755,14 +828,20 @@
       <c r="J10" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -781,14 +860,17 @@
       <c r="J11" t="s">
         <v>24</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
@@ -807,14 +889,20 @@
       <c r="J12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
@@ -833,14 +921,20 @@
       <c r="J13" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="K13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" t="s">
+        <v>24</v>
+      </c>
+      <c r="N13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>11</v>
       </c>
@@ -859,16 +953,24 @@
       <c r="J14" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="12" t="s">
+      <c r="K14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="13" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:H14"/>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="B1:C1"/>

--- a/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
+++ b/Capitulo999_INSTITUTO/Taller2_2026/Taller02_2026_ISGM.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="37">
   <si>
     <t>Apellido y Nombre</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>9 (Muy bien)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejercicio </t>
+  </si>
+  <si>
+    <t>Evaluación 3</t>
   </si>
 </sst>
 </file>
@@ -235,22 +241,22 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -533,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:O14"/>
+  <dimension ref="B1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -548,33 +554,40 @@
     <col min="11" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.85546875" customWidth="1"/>
     <col min="14" max="14" width="15.85546875" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="G1" s="10" t="s">
+      <c r="E1" s="10"/>
+      <c r="G1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="J1" s="10" t="s">
+      <c r="H1" s="13"/>
+      <c r="J1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="14" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-    </row>
-    <row r="2" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
@@ -593,18 +606,21 @@
       <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12" t="s">
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-    </row>
-    <row r="3" spans="2:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+    </row>
+    <row r="3" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="K3" s="1" t="s">
         <v>27</v>
       </c>
@@ -614,8 +630,11 @@
       <c r="N3" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="Q3" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -646,8 +665,14 @@
       <c r="N4" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -678,8 +703,14 @@
       <c r="N5" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -713,8 +744,14 @@
       <c r="N6" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -745,12 +782,18 @@
       <c r="N7" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -773,11 +816,17 @@
       <c r="L8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="M8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -805,8 +854,14 @@
       <c r="M9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
@@ -840,8 +895,14 @@
       <c r="N10" s="5" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -869,8 +930,14 @@
       <c r="M11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P11" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
@@ -889,20 +956,26 @@
       <c r="J12" t="s">
         <v>25</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="K12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
@@ -933,8 +1006,14 @@
       <c r="N13" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="P13" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>11</v>
       </c>
@@ -953,29 +1032,37 @@
       <c r="J14" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="13" t="s">
+      <c r="K14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="7" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B2:H14"/>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="P1:R1"/>
+    <mergeCell ref="P2:R2"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="J1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
